--- a/vnop_product_portal/static/xlsx/intem_template.xlsx
+++ b/vnop_product_portal/static/xlsx/intem_template.xlsx
@@ -1065,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="43.7777777777778" customWidth="1" min="1" max="1"/>
@@ -1079,87 +1079,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>QrWarranty</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Qr</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Cid</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>TradeMark</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Serial</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Use</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Preserve</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
